--- a/lesson2-advanced-data-analysis/linear-regression-walkthrough.xlsx
+++ b/lesson2-advanced-data-analysis/linear-regression-walkthrough.xlsx
@@ -1,12 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903DC156-2FA4-4E26-AD0E-FC1B2FB3D7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="1590" yWindow="900" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -22,15 +44,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -41,36 +64,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -260,17 +290,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B79"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -278,559 +311,626 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>54900.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>54900</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1">
-        <v>54300.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>54300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B4" s="1">
-        <v>54150.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>54150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B5" s="1">
-        <v>53976.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>53976</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B6" s="1">
-        <v>53723.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>53723</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B7" s="1">
-        <v>53580.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>53580</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B8" s="1">
-        <v>53443.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>53443</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B9" s="1">
-        <v>53395.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>53395</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B10" s="1">
-        <v>52997.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>52997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B11" s="1">
-        <v>52853.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>52853</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B12" s="1">
-        <v>52293.0</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>52293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B13" s="1">
-        <v>52211.0</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>52211</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B14" s="1">
-        <v>52143.0</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>52143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B15" s="1">
-        <v>52086.0</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>52086</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B16" s="1">
-        <v>51871.0</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>51871</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B17" s="1">
-        <v>51839.0</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>51839</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B18" s="1">
-        <v>51511.0</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>51511</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B19" s="1">
-        <v>51259.0</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>51259</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B20" s="1">
-        <v>50954.0</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>50954</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B21" s="1">
-        <v>50894.0</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>50894</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B22" s="1">
-        <v>50666.0</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>50666</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B23" s="1">
-        <v>50499.0</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>50499</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B24" s="1">
-        <v>50497.0</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>50497</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>0.06667</v>
+        <v>6.6669999999999993E-2</v>
       </c>
       <c r="B25" s="1">
-        <v>53354.0</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>53354</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>0.06667</v>
+        <v>6.6669999999999993E-2</v>
       </c>
       <c r="B26" s="1">
-        <v>53314.0</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>53314</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>0.06667</v>
+        <v>6.6669999999999993E-2</v>
       </c>
       <c r="B27" s="1">
-        <v>53286.0</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>53286</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>0.06667</v>
+        <v>6.6669999999999993E-2</v>
       </c>
       <c r="B28" s="1">
-        <v>52806.0</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>52806</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>0.06667</v>
+        <v>6.6669999999999993E-2</v>
       </c>
       <c r="B29" s="1">
-        <v>52372.0</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>52372</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>0.06667</v>
+        <v>6.6669999999999993E-2</v>
       </c>
       <c r="B30" s="1">
-        <v>49358.0</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>49358</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>0.1</v>
       </c>
       <c r="B31" s="1">
-        <v>52691.0</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>52691</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>0.1</v>
       </c>
       <c r="B32" s="1">
-        <v>52539.0</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>52539</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>0.1</v>
       </c>
       <c r="B33" s="1">
-        <v>51844.0</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>51844</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>0.1</v>
       </c>
       <c r="B34" s="1">
-        <v>51588.0</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>51588</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>0.1</v>
       </c>
       <c r="B35" s="1">
-        <v>51141.0</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>51141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>0.1</v>
       </c>
       <c r="B36" s="1">
-        <v>51015.0</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>51015</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>0.1</v>
       </c>
       <c r="B37" s="1">
-        <v>49923.0</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>49923</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>0.1</v>
       </c>
       <c r="B38" s="1">
-        <v>49521.0</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>49521</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>0.1</v>
       </c>
       <c r="B39" s="1">
-        <v>49315.0</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>49315</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>0.1</v>
       </c>
       <c r="B40" s="1">
-        <v>48625.0</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>48625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>0.13333</v>
       </c>
       <c r="B41" s="1">
-        <v>53210.0</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>53210</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>0.13333</v>
       </c>
       <c r="B42" s="1">
-        <v>52912.0</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>52912</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>0.13333</v>
       </c>
       <c r="B43" s="1">
-        <v>52373.0</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>52373</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>0.13333</v>
       </c>
       <c r="B44" s="1">
-        <v>50788.0</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>50788</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>0.13333</v>
       </c>
       <c r="B45" s="1">
-        <v>50375.0</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>50375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>0.13333</v>
       </c>
       <c r="B46" s="1">
-        <v>49840.0</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>49840</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>0.13333</v>
       </c>
       <c r="B47" s="1">
-        <v>49506.0</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>49506</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>0.13333</v>
       </c>
       <c r="B48" s="1">
-        <v>48428.0</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>48428</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>0.2</v>
       </c>
       <c r="B49" s="1">
-        <v>51680.0</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>51680</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>0.2</v>
       </c>
       <c r="B50" s="1">
-        <v>50451.0</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>50451</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>0.2</v>
       </c>
       <c r="B51" s="1">
-        <v>50109.0</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>50109</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>0.2</v>
       </c>
       <c r="B52" s="1">
-        <v>49337.0</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>49337</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>0.2</v>
       </c>
       <c r="B53" s="1">
-        <v>49312.0</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>49312</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>0.2</v>
       </c>
       <c r="B54" s="1">
-        <v>49179.0</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>49179</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>0.2</v>
       </c>
       <c r="B55" s="1">
-        <v>48701.0</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>48701</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>0.2</v>
       </c>
       <c r="B56" s="1">
-        <v>48675.0</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>48675</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>0.2</v>
       </c>
       <c r="B57" s="1">
-        <v>48360.0</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>48360</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>0.25</v>
       </c>
       <c r="B58" s="1">
-        <v>49440.0</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>49440</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>0.25</v>
       </c>
       <c r="B59" s="1">
-        <v>48892.0</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>48892</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>0.35</v>
       </c>
       <c r="B60" s="1">
-        <v>45274.0</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>45274</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>0.5</v>
       </c>
       <c r="B61" s="1">
-        <v>44595.0</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>44595</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>0.75</v>
       </c>
       <c r="B62" s="1">
-        <v>42104.0</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>42104</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>0.75</v>
       </c>
       <c r="B63" s="1">
-        <v>40796.0</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>40796</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>0.84</v>
       </c>
       <c r="B64" s="1">
-        <v>37748.0</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>37748</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>0.9</v>
       </c>
       <c r="B65" s="1">
-        <v>38486.0</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>38486</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>1.25</v>
       </c>
       <c r="B66" s="1">
-        <v>38921.0</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>38921</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>1.25</v>
       </c>
       <c r="B67" s="1">
-        <v>34728.0</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>34728</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>1.25</v>
       </c>
       <c r="B68" s="1">
-        <v>33369.0</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>33369</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>1.25</v>
       </c>
       <c r="B69" s="1">
-        <v>31039.0</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>31039</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>1.25</v>
       </c>
       <c r="B70" s="1">
-        <v>27259.0</v>
-      </c>
+        <v>27259</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>0.72509999999999997</v>
+      </c>
+      <c r="B71">
+        <v>39524</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>0.72509999999999997</v>
+      </c>
+      <c r="B72">
+        <v>39524</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>0.72509999999999997</v>
+      </c>
+      <c r="B73">
+        <v>39524</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>0.72509999999999997</v>
+      </c>
+      <c r="B74">
+        <v>39524</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>0</v>
+      </c>
+      <c r="B75">
+        <v>42567</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>0</v>
+      </c>
+      <c r="B76">
+        <v>42567</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>0.9</v>
+      </c>
+      <c r="B77">
+        <v>54755</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>0.9</v>
+      </c>
+      <c r="B78">
+        <v>54755</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>